--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Complaints/ComplaintsJournalReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Complaints/ComplaintsJournalReport.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vodovoz\repo\vodovoz_03\Source\Applications\Desktop\Vodovoz\bin\DebugWin\Reports\Complaints\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\VodovozSlot-3\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Complaints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958BDDFD-F6DE-4E5C-9473-ACA047B08557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FCB4F9-8BA6-42B2-B207-C84698501C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Rows">Лист1!$A$4:$U$5</definedName>
+    <definedName name="Rows">Лист1!$A$4:$V$5</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Отчёт по рекламациям</t>
   </si>
@@ -157,13 +157,19 @@
   </si>
   <si>
     <t>{{item.ResultCommentsAuthors}}</t>
+  </si>
+  <si>
+    <t>Последний заказ</t>
+  </si>
+  <si>
+    <t>{{item.LastOrderId}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -192,6 +198,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -201,7 +213,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -224,11 +236,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -253,6 +278,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,7 +627,7 @@
     <col min="1028" max="16384" width="10.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -621,7 +652,7 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="58.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="58.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -685,8 +716,11 @@
       <c r="U3" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="V3" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
@@ -750,8 +784,11 @@
       <c r="U4" s="6" t="s">
         <v>36</v>
       </c>
+      <c r="V4" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="5" spans="1:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:22" ht="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="54" fitToHeight="10000" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
